--- a/precios/precios-supermercados.xlsx
+++ b/precios/precios-supermercados.xlsx
@@ -5,6 +5,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cómo rellenar" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Precios" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Otros súper" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -16,7 +17,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.00&quot; €&quot;"/>
     <numFmt numFmtId="165" formatCode="0.00&quot; €&quot;"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,8 +78,12 @@
       <family val="2"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -98,6 +103,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F7A5A"/>
       </patternFill>
     </fill>
   </fills>
@@ -135,7 +145,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -233,6 +243,7 @@
     <xf numFmtId="165" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0"/>
@@ -9900,7 +9911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" style="17" min="1" max="1"/>
@@ -10028,6 +10039,20 @@
       <c r="A20" s="22" t="inlineStr">
         <is>
           <t>Precios orientativos según fuente, zona y disponibilidad. Pueden cambiar; las ofertas de Aldi incluidas finalizan el 04/10/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Hoja «Otros súper»: precios de cualquier otra cadena o tienda (una fila por precio). Columnas: producto (nombre del catálogo), súper, precio, ud/kg/l, formato, producto consultado, desde, hasta, nota y URL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Family Cash (05/10/2026): 102 precios del folleto del 7 al 27 de septiembre de 2026, ya caducado; orientativos.</t>
         </is>
       </c>
     </row>
@@ -26055,4 +26080,5106 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J103"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" style="17" min="1" max="1"/>
+    <col width="14" customWidth="1" style="17" min="2" max="2"/>
+    <col width="9" customWidth="1" style="17" min="3" max="3"/>
+    <col width="10" customWidth="1" style="17" min="4" max="4"/>
+    <col width="14" customWidth="1" style="17" min="5" max="5"/>
+    <col width="48" customWidth="1" style="17" min="6" max="6"/>
+    <col width="12" customWidth="1" style="17" min="7" max="7"/>
+    <col width="12" customWidth="1" style="17" min="8" max="8"/>
+    <col width="46" customWidth="1" style="17" min="9" max="9"/>
+    <col width="30" customWidth="1" style="17" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="33" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="B1" s="33" t="inlineStr">
+        <is>
+          <t>Súper</t>
+        </is>
+      </c>
+      <c r="C1" s="33" t="inlineStr">
+        <is>
+          <t>Precio</t>
+        </is>
+      </c>
+      <c r="D1" s="33" t="inlineStr">
+        <is>
+          <t>Precio por</t>
+        </is>
+      </c>
+      <c r="E1" s="33" t="inlineStr">
+        <is>
+          <t>Formato</t>
+        </is>
+      </c>
+      <c r="F1" s="33" t="inlineStr">
+        <is>
+          <t>Producto consultado</t>
+        </is>
+      </c>
+      <c r="G1" s="33" t="inlineStr">
+        <is>
+          <t>Desde</t>
+        </is>
+      </c>
+      <c r="H1" s="33" t="inlineStr">
+        <is>
+          <t>Hasta</t>
+        </is>
+      </c>
+      <c r="I1" s="33" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+      <c r="J1" s="33" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>Alioli</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr"/>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>Salsa Choví alioli (150-400 ml según variante)</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H2" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I2" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado; Formato según variante</t>
+        </is>
+      </c>
+      <c r="J2" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>Mayonesa</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>450 ml</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>Mayonesa Hellmann's</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J3" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>Tomate frito</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>390 g</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>Tomate frito Didi</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J4" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>Tomate triturado</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>400 g</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t>Tomate triturado Didi</t>
+        </is>
+      </c>
+      <c r="G5" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H5" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I5" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J5" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>Bebida isotónica</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>50 cl</t>
+        </is>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>Bebida isotónica Upgrade</t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H6" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I6" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>Cerveza</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>50 cl</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>Cerveza Estrella Galicia</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H7" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>Cerveza sin alcohol</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>33 cl</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>Cerveza Skol 0,0</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H8" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I8" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>Refresco de cola</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>33 cl</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>La Casera cola</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H9" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>Refresco de limón</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>33 cl</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>Kas limón</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H10" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I10" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t>Refresco de naranja</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>33 cl</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>Kas naranja</t>
+        </is>
+      </c>
+      <c r="G11" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H11" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I11" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>Vino blanco</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>Vino blanco verdejo Berberana Carta de Plata</t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H12" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I12" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t>Vino tinto</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>Vino tinto Berberana Carta de Plata</t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H13" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I13" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>Papilla de cereales</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>250 g</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>Papilla Nestlé 0,0% multicereales</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H14" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I14" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>Alitas de pollo</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr"/>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>Alas de pollo a granel</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H15" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I15" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t>Boquerones</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr"/>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>Boquerón congelado a granel</t>
+        </is>
+      </c>
+      <c r="G16" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H16" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I16" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado; Congelado</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t>Calamares</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr"/>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>Calamar patagónico a granel</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H17" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I17" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t>Carne picada</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>800 g</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>Preparado carne picada vacuno y cerdo</t>
+        </is>
+      </c>
+      <c r="G18" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H18" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I18" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t>Chuletas de cerdo</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr"/>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>Chuletas de aguja de cerdo Duroc con hueso</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H19" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I19" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t>Cordero</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr"/>
+      <c r="F20" s="0" t="inlineStr">
+        <is>
+          <t>Cordero a cuartos</t>
+        </is>
+      </c>
+      <c r="G20" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H20" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I20" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>Filetes de ternera</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr"/>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t>Filete babilla de vacuno</t>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H21" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I21" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t>Langostinos</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="D22" s="0" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E22" s="0" t="inlineStr"/>
+      <c r="F22" s="0" t="inlineStr">
+        <is>
+          <t>Langostino Vannamei crudo 30/40</t>
+        </is>
+      </c>
+      <c r="G22" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H22" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I22" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t>Pechuga de pollo</t>
+        </is>
+      </c>
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="D23" s="0" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E23" s="0" t="inlineStr"/>
+      <c r="F23" s="0" t="inlineStr">
+        <is>
+          <t>Pechuga de pollo entera (compra mínima 2 kg)</t>
+        </is>
+      </c>
+      <c r="G23" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H23" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I23" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t>Pollo entero</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="D24" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>1,2 kg</t>
+        </is>
+      </c>
+      <c r="F24" s="0" t="inlineStr">
+        <is>
+          <t>Pollo entero congelado</t>
+        </is>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H24" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I24" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado; Congelado</t>
+        </is>
+      </c>
+      <c r="J24" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t>Salmón</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="D25" s="0" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E25" s="0" t="inlineStr"/>
+      <c r="F25" s="0" t="inlineStr">
+        <is>
+          <t>Salmón entero o medios (2-3 kg)</t>
+        </is>
+      </c>
+      <c r="G25" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H25" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I25" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J25" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t>Sardinas</t>
+        </is>
+      </c>
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C26" s="0" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="D26" s="0" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E26" s="0" t="inlineStr"/>
+      <c r="F26" s="0" t="inlineStr">
+        <is>
+          <t>Sardina pequeña a granel</t>
+        </is>
+      </c>
+      <c r="G26" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H26" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I26" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J26" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t>Secreto ibérico</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C27" s="0" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="D27" s="0" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E27" s="0" t="inlineStr"/>
+      <c r="F27" s="0" t="inlineStr">
+        <is>
+          <t>Secreto de cerdo ibérico</t>
+        </is>
+      </c>
+      <c r="G27" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H27" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I27" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J27" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t>Sepia</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="D28" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t>880 g</t>
+        </is>
+      </c>
+      <c r="F28" s="0" t="inlineStr">
+        <is>
+          <t>Sepia limpia troceada MR Cold</t>
+        </is>
+      </c>
+      <c r="G28" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H28" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I28" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado; Congelado</t>
+        </is>
+      </c>
+      <c r="J28" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t>Chorizo</t>
+        </is>
+      </c>
+      <c r="B29" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C29" s="0" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="D29" s="0" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E29" s="0" t="inlineStr"/>
+      <c r="F29" s="0" t="inlineStr">
+        <is>
+          <t>Pan de chorizo Regio Oro (al corte)</t>
+        </is>
+      </c>
+      <c r="G29" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H29" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I29" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J29" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="inlineStr">
+        <is>
+          <t>Salchichón</t>
+        </is>
+      </c>
+      <c r="B30" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C30" s="0" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="D30" s="0" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E30" s="0" t="inlineStr"/>
+      <c r="F30" s="0" t="inlineStr">
+        <is>
+          <t>Pan de salchichón Regio Oro (al corte)</t>
+        </is>
+      </c>
+      <c r="G30" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H30" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I30" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J30" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t>Jamón cocido</t>
+        </is>
+      </c>
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="D31" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t>500 g</t>
+        </is>
+      </c>
+      <c r="F31" s="0" t="inlineStr">
+        <is>
+          <t>Jamón cocido sándwich lonchas Family</t>
+        </is>
+      </c>
+      <c r="G31" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H31" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I31" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J31" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t>Jamón serrano</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C32" s="0" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="D32" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t>380 g</t>
+        </is>
+      </c>
+      <c r="F32" s="0" t="inlineStr">
+        <is>
+          <t>Jamón serrano Turón</t>
+        </is>
+      </c>
+      <c r="G32" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H32" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I32" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J32" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
+        <is>
+          <t>Queso rallado</t>
+        </is>
+      </c>
+      <c r="B33" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C33" s="0" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="D33" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t>1 kg</t>
+        </is>
+      </c>
+      <c r="F33" s="0" t="inlineStr">
+        <is>
+          <t>Queso rallado 4 quesos Family</t>
+        </is>
+      </c>
+      <c r="G33" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H33" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I33" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J33" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="inlineStr">
+        <is>
+          <t>Pechuga de pavo</t>
+        </is>
+      </c>
+      <c r="B34" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C34" s="0" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="D34" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E34" s="0" t="inlineStr">
+        <is>
+          <t>100 g</t>
+        </is>
+      </c>
+      <c r="F34" s="0" t="inlineStr">
+        <is>
+          <t>Pechuguita de pavo asada Carretilla</t>
+        </is>
+      </c>
+      <c r="G34" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H34" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I34" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J34" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="inlineStr">
+        <is>
+          <t>Queso curado</t>
+        </is>
+      </c>
+      <c r="B35" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C35" s="0" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="D35" s="0" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E35" s="0" t="inlineStr"/>
+      <c r="F35" s="0" t="inlineStr">
+        <is>
+          <t>Queso de oveja viejo Don Ismael (al corte)</t>
+        </is>
+      </c>
+      <c r="G35" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H35" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I35" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J35" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="inlineStr">
+        <is>
+          <t>Queso de cabra</t>
+        </is>
+      </c>
+      <c r="B36" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C36" s="0" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="D36" s="0" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E36" s="0" t="inlineStr"/>
+      <c r="F36" s="0" t="inlineStr">
+        <is>
+          <t>Queso de cabra semicurado Don Ismael (al corte)</t>
+        </is>
+      </c>
+      <c r="G36" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H36" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I36" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J36" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="inlineStr">
+        <is>
+          <t>Queso semicurado</t>
+        </is>
+      </c>
+      <c r="B37" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C37" s="0" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="D37" s="0" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E37" s="0" t="inlineStr"/>
+      <c r="F37" s="0" t="inlineStr">
+        <is>
+          <t>Queso semicurado Escudo de Villalón (al corte)</t>
+        </is>
+      </c>
+      <c r="G37" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H37" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I37" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J37" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t>Helado</t>
+        </is>
+      </c>
+      <c r="B38" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C38" s="0" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D38" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E38" s="0" t="inlineStr">
+        <is>
+          <t>6 x 120 ml</t>
+        </is>
+      </c>
+      <c r="F38" s="0" t="inlineStr">
+        <is>
+          <t>Helado cono Family (surtido)</t>
+        </is>
+      </c>
+      <c r="G38" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H38" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I38" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J38" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="inlineStr">
+        <is>
+          <t>Patatas fritas congeladas</t>
+        </is>
+      </c>
+      <c r="B39" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C39" s="0" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="D39" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t>2,5 kg</t>
+        </is>
+      </c>
+      <c r="F39" s="0" t="inlineStr">
+        <is>
+          <t>Patatas 3/9 Family</t>
+        </is>
+      </c>
+      <c r="G39" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H39" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I39" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J39" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="inlineStr">
+        <is>
+          <t>Pizza congelada</t>
+        </is>
+      </c>
+      <c r="B40" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C40" s="0" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="D40" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
+        <is>
+          <t>250 g</t>
+        </is>
+      </c>
+      <c r="F40" s="0" t="inlineStr">
+        <is>
+          <t>Pizza snacks (surtido)</t>
+        </is>
+      </c>
+      <c r="G40" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H40" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I40" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J40" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="inlineStr">
+        <is>
+          <t>Verduras congeladas</t>
+        </is>
+      </c>
+      <c r="B41" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C41" s="0" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D41" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t>1 kg</t>
+        </is>
+      </c>
+      <c r="F41" s="0" t="inlineStr">
+        <is>
+          <t>Mezcla brócoli y apio</t>
+        </is>
+      </c>
+      <c r="G41" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H41" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I41" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J41" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="inlineStr">
+        <is>
+          <t>Aceitunas</t>
+        </is>
+      </c>
+      <c r="B42" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C42" s="0" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="D42" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t>3 x 150 g</t>
+        </is>
+      </c>
+      <c r="F42" s="0" t="inlineStr">
+        <is>
+          <t>Aceituna rellena de anchoa Family Tapas (peso escurrido)</t>
+        </is>
+      </c>
+      <c r="G42" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H42" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I42" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J42" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="inlineStr">
+        <is>
+          <t>Alcachofas en conserva</t>
+        </is>
+      </c>
+      <c r="B43" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C43" s="0" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="D43" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t>165 g</t>
+        </is>
+      </c>
+      <c r="F43" s="0" t="inlineStr">
+        <is>
+          <t>Alcachofa entera 8-12 Family (peso escurrido)</t>
+        </is>
+      </c>
+      <c r="G43" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H43" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I43" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J43" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="inlineStr">
+        <is>
+          <t>Atún en lata</t>
+        </is>
+      </c>
+      <c r="B44" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C44" s="0" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="D44" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>6 x 54 g</t>
+        </is>
+      </c>
+      <c r="F44" s="0" t="inlineStr">
+        <is>
+          <t>Atún claro en aceite de girasol Family (peso escurrido)</t>
+        </is>
+      </c>
+      <c r="G44" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H44" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I44" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J44" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="inlineStr">
+        <is>
+          <t>Espárragos</t>
+        </is>
+      </c>
+      <c r="B45" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C45" s="0" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="D45" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t>205 g</t>
+        </is>
+      </c>
+      <c r="F45" s="0" t="inlineStr">
+        <is>
+          <t>Espárrago blanco extra 6-9 Family (peso escurrido)</t>
+        </is>
+      </c>
+      <c r="G45" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H45" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I45" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J45" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="inlineStr">
+        <is>
+          <t>Maíz en lata</t>
+        </is>
+      </c>
+      <c r="B46" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C46" s="0" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D46" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
+        <is>
+          <t>285 g</t>
+        </is>
+      </c>
+      <c r="F46" s="0" t="inlineStr">
+        <is>
+          <t>Maíz dulce Family (peso escurrido)</t>
+        </is>
+      </c>
+      <c r="G46" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H46" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I46" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J46" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="inlineStr">
+        <is>
+          <t>Mejillones en escabeche</t>
+        </is>
+      </c>
+      <c r="B47" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C47" s="0" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D47" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E47" s="0" t="inlineStr">
+        <is>
+          <t>69 g</t>
+        </is>
+      </c>
+      <c r="F47" s="0" t="inlineStr">
+        <is>
+          <t>Mejillones en escabeche pequeños Didi</t>
+        </is>
+      </c>
+      <c r="G47" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H47" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I47" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J47" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="inlineStr">
+        <is>
+          <t>Pimientos del piquillo</t>
+        </is>
+      </c>
+      <c r="B48" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C48" s="0" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D48" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E48" s="0" t="inlineStr">
+        <is>
+          <t>220 g</t>
+        </is>
+      </c>
+      <c r="F48" s="0" t="inlineStr">
+        <is>
+          <t>Pimiento del piquillo Didi</t>
+        </is>
+      </c>
+      <c r="G48" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H48" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I48" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J48" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="inlineStr">
+        <is>
+          <t>Sardinas en lata</t>
+        </is>
+      </c>
+      <c r="B49" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C49" s="0" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D49" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E49" s="0" t="inlineStr">
+        <is>
+          <t>90 g</t>
+        </is>
+      </c>
+      <c r="F49" s="0" t="inlineStr">
+        <is>
+          <t>Sardinas en aceite de oliva Didi</t>
+        </is>
+      </c>
+      <c r="G49" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H49" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I49" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J49" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="inlineStr">
+        <is>
+          <t>Café en cápsulas</t>
+        </is>
+      </c>
+      <c r="B50" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C50" s="0" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="D50" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E50" s="0" t="inlineStr">
+        <is>
+          <t>30 cápsulas</t>
+        </is>
+      </c>
+      <c r="F50" s="0" t="inlineStr">
+        <is>
+          <t>Café Family compatible Dolce Gusto</t>
+        </is>
+      </c>
+      <c r="G50" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H50" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I50" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J50" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="inlineStr">
+        <is>
+          <t>Café molido</t>
+        </is>
+      </c>
+      <c r="B51" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C51" s="0" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="D51" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E51" s="0" t="inlineStr">
+        <is>
+          <t>250 g</t>
+        </is>
+      </c>
+      <c r="F51" s="0" t="inlineStr">
+        <is>
+          <t>Café molido natural o mezcla Saimaza</t>
+        </is>
+      </c>
+      <c r="G51" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H51" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I51" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J51" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0" t="inlineStr">
+        <is>
+          <t>Café soluble</t>
+        </is>
+      </c>
+      <c r="B52" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C52" s="0" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="D52" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E52" s="0" t="inlineStr">
+        <is>
+          <t>200 g</t>
+        </is>
+      </c>
+      <c r="F52" s="0" t="inlineStr">
+        <is>
+          <t>Nescafé (surtido)</t>
+        </is>
+      </c>
+      <c r="G52" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H52" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I52" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J52" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0" t="inlineStr">
+        <is>
+          <t>Cereales</t>
+        </is>
+      </c>
+      <c r="B53" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C53" s="0" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="D53" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E53" s="0" t="inlineStr">
+        <is>
+          <t>330 g</t>
+        </is>
+      </c>
+      <c r="F53" s="0" t="inlineStr">
+        <is>
+          <t>Cereales Kellogg's (surtido)</t>
+        </is>
+      </c>
+      <c r="G53" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H53" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I53" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J53" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="0" t="inlineStr">
+        <is>
+          <t>Chocolate</t>
+        </is>
+      </c>
+      <c r="B54" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C54" s="0" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D54" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E54" s="0" t="inlineStr">
+        <is>
+          <t>150 g</t>
+        </is>
+      </c>
+      <c r="F54" s="0" t="inlineStr">
+        <is>
+          <t>Chocolate Clavileño (surtido)</t>
+        </is>
+      </c>
+      <c r="G54" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H54" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I54" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J54" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0" t="inlineStr">
+        <is>
+          <t>Chucherías</t>
+        </is>
+      </c>
+      <c r="B55" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C55" s="0" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D55" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E55" s="0" t="inlineStr">
+        <is>
+          <t>1 kg</t>
+        </is>
+      </c>
+      <c r="F55" s="0" t="inlineStr">
+        <is>
+          <t>Gominolas Damel (surtido)</t>
+        </is>
+      </c>
+      <c r="G55" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H55" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I55" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J55" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0" t="inlineStr">
+        <is>
+          <t>Frutos secos</t>
+        </is>
+      </c>
+      <c r="B56" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C56" s="0" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="D56" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E56" s="0" t="inlineStr">
+        <is>
+          <t>175 g</t>
+        </is>
+      </c>
+      <c r="F56" s="0" t="inlineStr">
+        <is>
+          <t>Nuez mitades</t>
+        </is>
+      </c>
+      <c r="G56" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H56" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I56" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J56" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0" t="inlineStr">
+        <is>
+          <t>Galletas</t>
+        </is>
+      </c>
+      <c r="B57" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C57" s="0" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="D57" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E57" s="0" t="inlineStr">
+        <is>
+          <t>6 x 200 g</t>
+        </is>
+      </c>
+      <c r="F57" s="0" t="inlineStr">
+        <is>
+          <t>Galletas Family Biscuits (surtido)</t>
+        </is>
+      </c>
+      <c r="G57" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H57" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I57" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J57" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0" t="inlineStr">
+        <is>
+          <t>Mermelada</t>
+        </is>
+      </c>
+      <c r="B58" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C58" s="0" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="D58" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E58" s="0" t="inlineStr">
+        <is>
+          <t>240 g</t>
+        </is>
+      </c>
+      <c r="F58" s="0" t="inlineStr">
+        <is>
+          <t>Mermelada Antiu Xixona (surtido)</t>
+        </is>
+      </c>
+      <c r="G58" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H58" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I58" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J58" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="0" t="inlineStr">
+        <is>
+          <t>Champiñones</t>
+        </is>
+      </c>
+      <c r="B59" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C59" s="0" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D59" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E59" s="0" t="inlineStr">
+        <is>
+          <t>300 g</t>
+        </is>
+      </c>
+      <c r="F59" s="0" t="inlineStr">
+        <is>
+          <t>Champiñón entero, bandeja</t>
+        </is>
+      </c>
+      <c r="G59" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H59" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I59" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J59" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="0" t="inlineStr">
+        <is>
+          <t>Ensalada en bolsa</t>
+        </is>
+      </c>
+      <c r="B60" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C60" s="0" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D60" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E60" s="0" t="inlineStr">
+        <is>
+          <t>250 g</t>
+        </is>
+      </c>
+      <c r="F60" s="0" t="inlineStr">
+        <is>
+          <t>Ensalada 4 estaciones Family</t>
+        </is>
+      </c>
+      <c r="G60" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H60" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I60" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J60" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0" t="inlineStr">
+        <is>
+          <t>Patata</t>
+        </is>
+      </c>
+      <c r="B61" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C61" s="0" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="D61" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E61" s="0" t="inlineStr">
+        <is>
+          <t>10 kg</t>
+        </is>
+      </c>
+      <c r="F61" s="0" t="inlineStr">
+        <is>
+          <t>Patatas, saco</t>
+        </is>
+      </c>
+      <c r="G61" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H61" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I61" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J61" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="B62" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C62" s="0" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="D62" s="0" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E62" s="0" t="inlineStr"/>
+      <c r="F62" s="0" t="inlineStr">
+        <is>
+          <t>Tomate pera a granel</t>
+        </is>
+      </c>
+      <c r="G62" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H62" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I62" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J62" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="inlineStr">
+        <is>
+          <t>Uvas</t>
+        </is>
+      </c>
+      <c r="B63" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C63" s="0" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="D63" s="0" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E63" s="0" t="inlineStr"/>
+      <c r="F63" s="0" t="inlineStr">
+        <is>
+          <t>Uva blanca a granel</t>
+        </is>
+      </c>
+      <c r="G63" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H63" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I63" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J63" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0" t="inlineStr">
+        <is>
+          <t>Zanahoria</t>
+        </is>
+      </c>
+      <c r="B64" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C64" s="0" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D64" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E64" s="0" t="inlineStr">
+        <is>
+          <t>1 kg</t>
+        </is>
+      </c>
+      <c r="F64" s="0" t="inlineStr">
+        <is>
+          <t>Zanahoria, bolsa</t>
+        </is>
+      </c>
+      <c r="G64" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H64" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I64" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J64" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0" t="inlineStr">
+        <is>
+          <t>Champú</t>
+        </is>
+      </c>
+      <c r="B65" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C65" s="0" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="D65" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E65" s="0" t="inlineStr">
+        <is>
+          <t>625 ml</t>
+        </is>
+      </c>
+      <c r="F65" s="0" t="inlineStr">
+        <is>
+          <t>Champú Pantene</t>
+        </is>
+      </c>
+      <c r="G65" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H65" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I65" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J65" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0" t="inlineStr">
+        <is>
+          <t>Desodorante</t>
+        </is>
+      </c>
+      <c r="B66" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C66" s="0" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="D66" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E66" s="0" t="inlineStr">
+        <is>
+          <t>2 x 200 ml</t>
+        </is>
+      </c>
+      <c r="F66" s="0" t="inlineStr">
+        <is>
+          <t>Desodorante spray Nivea Black &amp; White</t>
+        </is>
+      </c>
+      <c r="G66" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H66" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I66" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J66" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0" t="inlineStr">
+        <is>
+          <t>Gel de ducha</t>
+        </is>
+      </c>
+      <c r="B67" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C67" s="0" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="D67" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E67" s="0" t="inlineStr">
+        <is>
+          <t>1250 ml</t>
+        </is>
+      </c>
+      <c r="F67" s="0" t="inlineStr">
+        <is>
+          <t>Gel Family Care</t>
+        </is>
+      </c>
+      <c r="G67" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H67" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I67" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J67" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0" t="inlineStr">
+        <is>
+          <t>Jabón de manos</t>
+        </is>
+      </c>
+      <c r="B68" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C68" s="0" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D68" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E68" s="0" t="inlineStr">
+        <is>
+          <t>500 ml</t>
+        </is>
+      </c>
+      <c r="F68" s="0" t="inlineStr">
+        <is>
+          <t>Jabón de manos (surtido)</t>
+        </is>
+      </c>
+      <c r="G68" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H68" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I68" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J68" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0" t="inlineStr">
+        <is>
+          <t>Pasta de dientes</t>
+        </is>
+      </c>
+      <c r="B69" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C69" s="0" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="D69" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E69" s="0" t="inlineStr">
+        <is>
+          <t>75 ml</t>
+        </is>
+      </c>
+      <c r="F69" s="0" t="inlineStr">
+        <is>
+          <t>Dentífrico Parodontax</t>
+        </is>
+      </c>
+      <c r="G69" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H69" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I69" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J69" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0" t="inlineStr">
+        <is>
+          <t>Alfombra</t>
+        </is>
+      </c>
+      <c r="B70" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C70" s="0" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="D70" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E70" s="0" t="inlineStr">
+        <is>
+          <t>1 ud</t>
+        </is>
+      </c>
+      <c r="F70" s="0" t="inlineStr">
+        <is>
+          <t>Alfombra interior poliéster 40 x 60 cm</t>
+        </is>
+      </c>
+      <c r="G70" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H70" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I70" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J70" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="0" t="inlineStr">
+        <is>
+          <t>Almohada</t>
+        </is>
+      </c>
+      <c r="B71" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C71" s="0" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="D71" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E71" s="0" t="inlineStr">
+        <is>
+          <t>1 ud</t>
+        </is>
+      </c>
+      <c r="F71" s="0" t="inlineStr">
+        <is>
+          <t>Almohada viscoelástica 70 cm</t>
+        </is>
+      </c>
+      <c r="G71" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H71" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I71" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado; Precio desde, según tamaño</t>
+        </is>
+      </c>
+      <c r="J71" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="0" t="inlineStr">
+        <is>
+          <t>Sartén</t>
+        </is>
+      </c>
+      <c r="B72" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C72" s="0" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="D72" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E72" s="0" t="inlineStr">
+        <is>
+          <t>1 ud</t>
+        </is>
+      </c>
+      <c r="F72" s="0" t="inlineStr">
+        <is>
+          <t>Sartén aluminio prensado Tierra 16 cm</t>
+        </is>
+      </c>
+      <c r="G72" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H72" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I72" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado; Precio desde, según tamaño</t>
+        </is>
+      </c>
+      <c r="J72" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="0" t="inlineStr">
+        <is>
+          <t>Sábanas</t>
+        </is>
+      </c>
+      <c r="B73" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C73" s="0" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="D73" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E73" s="0" t="inlineStr">
+        <is>
+          <t>1 ud</t>
+        </is>
+      </c>
+      <c r="F73" s="0" t="inlineStr">
+        <is>
+          <t>Bajera microfibra 90 cm</t>
+        </is>
+      </c>
+      <c r="G73" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H73" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I73" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado; Precio desde, según tamaño</t>
+        </is>
+      </c>
+      <c r="J73" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0" t="inlineStr">
+        <is>
+          <t>Toallas</t>
+        </is>
+      </c>
+      <c r="B74" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C74" s="0" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D74" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E74" s="0" t="inlineStr">
+        <is>
+          <t>1 ud</t>
+        </is>
+      </c>
+      <c r="F74" s="0" t="inlineStr">
+        <is>
+          <t>Toalla 100% algodón</t>
+        </is>
+      </c>
+      <c r="G74" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H74" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I74" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado; Precio desde, según tamaño</t>
+        </is>
+      </c>
+      <c r="J74" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0" t="inlineStr">
+        <is>
+          <t>Vasos</t>
+        </is>
+      </c>
+      <c r="B75" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C75" s="0" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="D75" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E75" s="0" t="inlineStr">
+        <is>
+          <t>6 ud</t>
+        </is>
+      </c>
+      <c r="F75" s="0" t="inlineStr">
+        <is>
+          <t>Vaso Thian Greencook</t>
+        </is>
+      </c>
+      <c r="G75" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H75" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I75" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J75" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="0" t="inlineStr">
+        <is>
+          <t>Detergente</t>
+        </is>
+      </c>
+      <c r="B76" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C76" s="0" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="D76" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E76" s="0" t="inlineStr">
+        <is>
+          <t>46 lavados</t>
+        </is>
+      </c>
+      <c r="F76" s="0" t="inlineStr">
+        <is>
+          <t>Lavandera cápsulas 4 en 1</t>
+        </is>
+      </c>
+      <c r="G76" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H76" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I76" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J76" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="0" t="inlineStr">
+        <is>
+          <t>Friegasuelos</t>
+        </is>
+      </c>
+      <c r="B77" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C77" s="0" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D77" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E77" s="0" t="inlineStr">
+        <is>
+          <t>1 l</t>
+        </is>
+      </c>
+      <c r="F77" s="0" t="inlineStr">
+        <is>
+          <t>Friegasuelos Mister Brillo</t>
+        </is>
+      </c>
+      <c r="G77" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H77" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I77" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J77" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="0" t="inlineStr">
+        <is>
+          <t>Lavavajillas a mano</t>
+        </is>
+      </c>
+      <c r="B78" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C78" s="0" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="D78" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E78" s="0" t="inlineStr">
+        <is>
+          <t>1,5 l</t>
+        </is>
+      </c>
+      <c r="F78" s="0" t="inlineStr">
+        <is>
+          <t>Lavavajillas limón Tejón</t>
+        </is>
+      </c>
+      <c r="G78" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H78" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I78" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J78" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="0" t="inlineStr">
+        <is>
+          <t>Suavizante</t>
+        </is>
+      </c>
+      <c r="B79" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C79" s="0" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D79" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E79" s="0" t="inlineStr">
+        <is>
+          <t>50 lavados</t>
+        </is>
+      </c>
+      <c r="F79" s="0" t="inlineStr">
+        <is>
+          <t>Suavizante Disiclin</t>
+        </is>
+      </c>
+      <c r="G79" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H79" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I79" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J79" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0" t="inlineStr">
+        <is>
+          <t>Batidos</t>
+        </is>
+      </c>
+      <c r="B80" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C80" s="0" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="D80" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E80" s="0" t="inlineStr">
+        <is>
+          <t>6 x 200 ml</t>
+        </is>
+      </c>
+      <c r="F80" s="0" t="inlineStr">
+        <is>
+          <t>Batido Puleva (surtido)</t>
+        </is>
+      </c>
+      <c r="G80" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H80" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I80" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J80" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="0" t="inlineStr">
+        <is>
+          <t>Bebida de avena</t>
+        </is>
+      </c>
+      <c r="B81" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C81" s="0" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D81" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E81" s="0" t="inlineStr">
+        <is>
+          <t>1 l</t>
+        </is>
+      </c>
+      <c r="F81" s="0" t="inlineStr">
+        <is>
+          <t>Bebida de avena Alpro</t>
+        </is>
+      </c>
+      <c r="G81" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H81" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I81" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J81" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="0" t="inlineStr">
+        <is>
+          <t>Bebida de soja</t>
+        </is>
+      </c>
+      <c r="B82" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C82" s="0" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D82" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E82" s="0" t="inlineStr">
+        <is>
+          <t>1 l</t>
+        </is>
+      </c>
+      <c r="F82" s="0" t="inlineStr">
+        <is>
+          <t>Bebida de soja Family</t>
+        </is>
+      </c>
+      <c r="G82" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H82" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I82" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J82" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="0" t="inlineStr">
+        <is>
+          <t>Huevos</t>
+        </is>
+      </c>
+      <c r="B83" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C83" s="0" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="D83" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E83" s="0" t="inlineStr">
+        <is>
+          <t>12 ud</t>
+        </is>
+      </c>
+      <c r="F83" s="0" t="inlineStr">
+        <is>
+          <t>Huevos M Ovocity (docena)</t>
+        </is>
+      </c>
+      <c r="G83" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H83" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I83" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J83" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="0" t="inlineStr">
+        <is>
+          <t>Kéfir</t>
+        </is>
+      </c>
+      <c r="B84" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C84" s="0" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="D84" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E84" s="0" t="inlineStr">
+        <is>
+          <t>500 g</t>
+        </is>
+      </c>
+      <c r="F84" s="0" t="inlineStr">
+        <is>
+          <t>Kéfir líquido natural Margui</t>
+        </is>
+      </c>
+      <c r="G84" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H84" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I84" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J84" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="0" t="inlineStr">
+        <is>
+          <t>Mantequilla</t>
+        </is>
+      </c>
+      <c r="B85" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C85" s="0" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="D85" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E85" s="0" t="inlineStr">
+        <is>
+          <t>250 g</t>
+        </is>
+      </c>
+      <c r="F85" s="0" t="inlineStr">
+        <is>
+          <t>Mantequilla Lattena</t>
+        </is>
+      </c>
+      <c r="G85" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H85" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I85" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J85" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="0" t="inlineStr">
+        <is>
+          <t>Magdalenas</t>
+        </is>
+      </c>
+      <c r="B86" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C86" s="0" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D86" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E86" s="0" t="inlineStr">
+        <is>
+          <t>495 g</t>
+        </is>
+      </c>
+      <c r="F86" s="0" t="inlineStr">
+        <is>
+          <t>Magdalenas Dulces La Abuela</t>
+        </is>
+      </c>
+      <c r="G86" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H86" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I86" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J86" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="0" t="inlineStr">
+        <is>
+          <t>Pan de barra</t>
+        </is>
+      </c>
+      <c r="B87" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C87" s="0" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="D87" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E87" s="0" t="inlineStr">
+        <is>
+          <t>240 g</t>
+        </is>
+      </c>
+      <c r="F87" s="0" t="inlineStr">
+        <is>
+          <t>Barra panadera (comprando 3)</t>
+        </is>
+      </c>
+      <c r="G87" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H87" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I87" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J87" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="0" t="inlineStr">
+        <is>
+          <t>Pan integral</t>
+        </is>
+      </c>
+      <c r="B88" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C88" s="0" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="D88" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E88" s="0" t="inlineStr">
+        <is>
+          <t>450 g</t>
+        </is>
+      </c>
+      <c r="F88" s="0" t="inlineStr">
+        <is>
+          <t>Hogaza 100% integral</t>
+        </is>
+      </c>
+      <c r="G88" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H88" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I88" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J88" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="0" t="inlineStr">
+        <is>
+          <t>Agenda</t>
+        </is>
+      </c>
+      <c r="B89" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C89" s="0" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="D89" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E89" s="0" t="inlineStr">
+        <is>
+          <t>1 ud</t>
+        </is>
+      </c>
+      <c r="F89" s="0" t="inlineStr">
+        <is>
+          <t>Agenda escolar 26-27</t>
+        </is>
+      </c>
+      <c r="G89" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H89" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I89" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado; Precio desde</t>
+        </is>
+      </c>
+      <c r="J89" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="0" t="inlineStr">
+        <is>
+          <t>Bolígrafos</t>
+        </is>
+      </c>
+      <c r="B90" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C90" s="0" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D90" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E90" s="0" t="inlineStr">
+        <is>
+          <t>10 ud</t>
+        </is>
+      </c>
+      <c r="F90" s="0" t="inlineStr">
+        <is>
+          <t>Bic Cristal Soft</t>
+        </is>
+      </c>
+      <c r="G90" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H90" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I90" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J90" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="0" t="inlineStr">
+        <is>
+          <t>Carpetas</t>
+        </is>
+      </c>
+      <c r="B91" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C91" s="0" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="D91" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E91" s="0" t="inlineStr">
+        <is>
+          <t>1 ud</t>
+        </is>
+      </c>
+      <c r="F91" s="0" t="inlineStr">
+        <is>
+          <t>Carpeta Campus Soft A4 con 25 recambios</t>
+        </is>
+      </c>
+      <c r="G91" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H91" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I91" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J91" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="0" t="inlineStr">
+        <is>
+          <t>Cuaderno</t>
+        </is>
+      </c>
+      <c r="B92" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C92" s="0" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D92" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E92" s="0" t="inlineStr">
+        <is>
+          <t>1 ud</t>
+        </is>
+      </c>
+      <c r="F92" s="0" t="inlineStr">
+        <is>
+          <t>Bloc A4 tapa blanda Campus, 80 hojas</t>
+        </is>
+      </c>
+      <c r="G92" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H92" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I92" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J92" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="0" t="inlineStr">
+        <is>
+          <t>Estuche</t>
+        </is>
+      </c>
+      <c r="B93" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C93" s="0" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="D93" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E93" s="0" t="inlineStr">
+        <is>
+          <t>1 ud</t>
+        </is>
+      </c>
+      <c r="F93" s="0" t="inlineStr">
+        <is>
+          <t>Portatodo Oxford</t>
+        </is>
+      </c>
+      <c r="G93" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H93" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I93" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado; Precio desde</t>
+        </is>
+      </c>
+      <c r="J93" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="0" t="inlineStr">
+        <is>
+          <t>Folios</t>
+        </is>
+      </c>
+      <c r="B94" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C94" s="0" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D94" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E94" s="0" t="inlineStr">
+        <is>
+          <t>500 hojas</t>
+        </is>
+      </c>
+      <c r="F94" s="0" t="inlineStr">
+        <is>
+          <t>Folios A4 Campus 80 g</t>
+        </is>
+      </c>
+      <c r="G94" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H94" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I94" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J94" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="0" t="inlineStr">
+        <is>
+          <t>Lápices</t>
+        </is>
+      </c>
+      <c r="B95" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C95" s="0" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="D95" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E95" s="0" t="inlineStr">
+        <is>
+          <t>1 ud</t>
+        </is>
+      </c>
+      <c r="F95" s="0" t="inlineStr">
+        <is>
+          <t>Pack Staedtler 2 lápices Noris + boli y regla</t>
+        </is>
+      </c>
+      <c r="G95" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H95" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I95" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J95" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="0" t="inlineStr">
+        <is>
+          <t>Mochila</t>
+        </is>
+      </c>
+      <c r="B96" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C96" s="0" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="D96" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E96" s="0" t="inlineStr">
+        <is>
+          <t>1 ud</t>
+        </is>
+      </c>
+      <c r="F96" s="0" t="inlineStr">
+        <is>
+          <t>Mochila 17 pulgadas</t>
+        </is>
+      </c>
+      <c r="G96" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H96" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I96" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J96" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="0" t="inlineStr">
+        <is>
+          <t>Arroz largo</t>
+        </is>
+      </c>
+      <c r="B97" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C97" s="0" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D97" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E97" s="0" t="inlineStr">
+        <is>
+          <t>1 kg</t>
+        </is>
+      </c>
+      <c r="F97" s="0" t="inlineStr">
+        <is>
+          <t>Arroz largo extra Family</t>
+        </is>
+      </c>
+      <c r="G97" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H97" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I97" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J97" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="0" t="inlineStr">
+        <is>
+          <t>Arroz redondo</t>
+        </is>
+      </c>
+      <c r="B98" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C98" s="0" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D98" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E98" s="0" t="inlineStr">
+        <is>
+          <t>1 kg</t>
+        </is>
+      </c>
+      <c r="F98" s="0" t="inlineStr">
+        <is>
+          <t>Arroz redondo extra Family</t>
+        </is>
+      </c>
+      <c r="G98" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H98" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I98" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J98" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="0" t="inlineStr">
+        <is>
+          <t>Fideos</t>
+        </is>
+      </c>
+      <c r="B99" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C99" s="0" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D99" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E99" s="0" t="inlineStr">
+        <is>
+          <t>1 kg</t>
+        </is>
+      </c>
+      <c r="F99" s="0" t="inlineStr">
+        <is>
+          <t>Fideo nº 0 Family</t>
+        </is>
+      </c>
+      <c r="G99" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H99" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I99" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J99" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="0" t="inlineStr">
+        <is>
+          <t>Garbanzos cocidos</t>
+        </is>
+      </c>
+      <c r="B100" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C100" s="0" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D100" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E100" s="0" t="inlineStr">
+        <is>
+          <t>400 g</t>
+        </is>
+      </c>
+      <c r="F100" s="0" t="inlineStr">
+        <is>
+          <t>Garbanzos cocidos Didi (peso escurrido)</t>
+        </is>
+      </c>
+      <c r="G100" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H100" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I100" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J100" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="0" t="inlineStr">
+        <is>
+          <t>Lentejas cocidas</t>
+        </is>
+      </c>
+      <c r="B101" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C101" s="0" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D101" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E101" s="0" t="inlineStr">
+        <is>
+          <t>400 g</t>
+        </is>
+      </c>
+      <c r="F101" s="0" t="inlineStr">
+        <is>
+          <t>Lentejas cocidas Didi (peso escurrido)</t>
+        </is>
+      </c>
+      <c r="G101" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H101" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I101" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J101" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="0" t="inlineStr">
+        <is>
+          <t>Macarrones</t>
+        </is>
+      </c>
+      <c r="B102" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C102" s="0" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D102" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E102" s="0" t="inlineStr">
+        <is>
+          <t>1 kg</t>
+        </is>
+      </c>
+      <c r="F102" s="0" t="inlineStr">
+        <is>
+          <t>Macarrón Family</t>
+        </is>
+      </c>
+      <c r="G102" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H102" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I102" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J102" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="0" t="inlineStr">
+        <is>
+          <t>Tallarines</t>
+        </is>
+      </c>
+      <c r="B103" s="0" t="inlineStr">
+        <is>
+          <t>Family Cash</t>
+        </is>
+      </c>
+      <c r="C103" s="0" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D103" s="0" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E103" s="0" t="inlineStr">
+        <is>
+          <t>1 kg</t>
+        </is>
+      </c>
+      <c r="F103" s="0" t="inlineStr">
+        <is>
+          <t>Tallarín Family</t>
+        </is>
+      </c>
+      <c r="G103" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H103" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I103" s="0" t="inlineStr">
+        <is>
+          <t>Precio de folleto (oferta del 7 al 27 sept), ya caducado</t>
+        </is>
+      </c>
+      <c r="J103" s="0" t="inlineStr">
+        <is>
+          <t>https://familycash.folle.to/images/familycash/familycash-weekly-ad.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>